--- a/domain-behaviour/interim/Domain_Behaviour.xlsx
+++ b/domain-behaviour/interim/Domain_Behaviour.xlsx
@@ -23,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,77 +423,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Observation_Class</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Consumer_Class</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Consumer_Status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>BCs</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>DSSs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>BCs_Fanning_Out</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max_Fanout</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Primary_Axis</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Axes_Seen</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scale_Mix</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Share_With_Units</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Share_With_Specimen</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Share_With_Method</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Share_With_Location</t>
         </is>
@@ -852,12 +840,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>location 1</t>
+          <t>(none) 1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1528,12 +1516,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>location 1</t>
+          <t>(none) 1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1590,7 +1578,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>location 5; category 1</t>
+          <t>location 4; category 1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1801,12 +1789,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>category; evaluator</t>
+          <t>category</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>category 4; evaluator 4</t>
+          <t>category 4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1956,12 +1944,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>category 3</t>
+          <t>(none) 3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2013,12 +2001,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>evaluator</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>evaluator 4</t>
+          <t>(none) 4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2132,7 +2120,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>(none) 3; evaluator 2</t>
+          <t>(none) 5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2241,12 +2229,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>location 4</t>
+          <t>(none) 4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2278,36 +2266,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>bc_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>bc_short_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DSS_Count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Axes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Axes_Value_List_Only</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>DS_Codes</t>
         </is>
@@ -2337,7 +2330,8 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>AE; AEPRESP</t>
         </is>
@@ -2367,7 +2361,8 @@
           <t>category</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>CMFREE; CMPRESP; CMPRIORBREASTCANCER; CMPRIORCANCER</t>
         </is>
@@ -2394,10 +2389,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>location</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>EXPOSCOLL; EXPOSCOLL_XANOMELINEPLACEBO</t>
         </is>
@@ -2427,7 +2427,8 @@
           <t>method; test detail; scale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>TRNSCPTNFRAGCNT; TRNSCPTNGENTRNIND; TRNSCPTNNORMLVL; TRNSCPTNNORMLVLDIFF; TRNSCPTNPERCNTRANK</t>
         </is>
@@ -2457,7 +2458,8 @@
           <t>test detail</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>CPNUMVARALTEXON; CPNUMVARATIO; CPNUMVARINTP; CPNUMVARNUMGCPY</t>
         </is>
@@ -2487,7 +2489,8 @@
           <t>method; test detail; scale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>SNVGENOTYPE; SNVPRAMACHG; SNVPRCSEQCHG; SNVREADEPTH; SNVVAREADEPTHRD; SNVVARIMPCLASS</t>
         </is>
@@ -2517,7 +2520,8 @@
           <t>test detail</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>MICRISTBDETECT; MICRISTBOVRASTAT</t>
         </is>
@@ -2547,7 +2551,8 @@
           <t>test detail</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>GENESIGINTP; GENESIGSCORE</t>
         </is>
@@ -2577,7 +2582,8 @@
           <t>test detail; scale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>SHRTVAREADEPTH; SHRTVAREADEPTHRD; SHRTVARIMPCLASS; SHRTVARPRAMACHG; SHRTVARPRCSEQCHG</t>
         </is>
@@ -2607,7 +2613,8 @@
           <t>specimen; method; test detail; scale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>TMBNORMNUMSEQVAR; TMBNUMSEQVAR; TMBVARSEQBURDINTP</t>
         </is>
@@ -2637,7 +2644,8 @@
           <t>test detail</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>SEQREAREADDEPTH; SEQREARGENE1; SEQREARGENE2; SEQREARIMPCLASS; SEQREARPREINFRIND; SEQREARTYPE</t>
         </is>
@@ -2667,7 +2675,8 @@
           <t>method; test detail</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>VNTRNCAGRPT; VNTRNUCLSEQ; VNTRPNCAGRPT</t>
         </is>
@@ -2697,7 +2706,8 @@
           <t>test detail</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>VARPROFPRDIPLO; VARPROFPRPHENO</t>
         </is>
@@ -2727,7 +2737,8 @@
           <t>binding agent</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>MBIGGABAA; MBIGGABAF; MBIGGABAV; MBIGGABBB; MBIGGABC; MBIGGABCD; MBIGGABCP; MBIGGABCTE; MBIGGABCTR; MBIGGABCTT; MBIGGABCV; MBIGGABDV; MBIGGABEBVCA; MBIGGABEBVEDA; MBIGGABEBVENA1; MBIGGABHAV; MBIGGABHBVCA; MBIGGABHDV; MBIGGABHEV; MBIGGABHHV1; MBIGGABHHV2; MBIGGABHP; MBIGGABHPVB19; MBIGGABHSV; MBIGGABIAV; MBIGGABIBV; MBIGGABLP; MBIGGABMBTC; MBIGGABMM; MBIGGABMPP; MBIGGABMRV; MBIGGABNGLI4; MBIGGABPC; MBIGGABRV; MBIGGABSARSCV2; MBIGGABSG; MBIGGABSP; MBIGGABSPDST1; MBIGGABSPDST10A; MBIGGABSPDST11A; MBIGGABSPDST12F; MBIGGABSPDST14; MBIGGABSPDST15B; MBIGGABSPDST17F; MBIGGABSPDST18C; MBIGGABSPDST19A; MBIGGABSPDST19F; MBIGGABSPDST2; MBIGGABSPDST20A; MBIGGABSPDST22F; MBIGGABSPDST23F; MBIGGABSPDST3; MBIGGABSPDST33F; MBIGGABSPDST4; MBIGGABSPDST5; MBIGGABSPDST6B; MBIGGABSPDST7F; MBIGGABSPDST8; MBIGGABSPDST9N; MBIGGABSPDST9V; MBIGGABTG; MBIGGABVCTBSU; MBIGGABVZV</t>
         </is>
@@ -2757,7 +2768,8 @@
           <t>specimen; method; binding agent; test detail; scale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>ARIGEABAA; ARIGEABAAMAST7; ARIGEABAARAST; ARIGEABACA; ARIGEABACARAST; ARIGEABAF; ARIGEABAFRAST; ARIGEABAHDMA; ARIGEABAHDMARAST; ARIGEABAHDMMAST7; ARIGEABAMA; ARIGEABAMARAST; ARIGEABAMAST7; ARIGEABBEP; ARIGEABBEPRAST; ARIGEABBGP; ARIGEABBGPRAST; ARIGEABBMAST7; ARIGEABBMAST72; ARIGEABBMVA; ARIGEABBMVARAST; ARIGEABCA; ARIGEABCANA; ARIGEABCANARAST; ARIGEABCARAST; ARIGEABCBMAST7; ARIGEABCDA; ARIGEABCDARAST; ARIGEABCDMAST7; ARIGEABCH; ARIGEABCHRAST; ARIGEABCMA; ARIGEABCMARAST; ARIGEABCMAST7; ARIGEABCMIXA; ARIGEABCMIXARAST; ARIGEABCMMAST7; ARIGEABCNA; ARIGEABCNARAST; ARIGEABCPMAST7; ARIGEABCRP; ARIGEABCRPRAST; ARIGEABDDA; ARIGEABDDARAST; ARIGEABDDMAST7; ARIGEABEHDMA; ARIGEABEHDMARAST; ARIGEABEPP; ARIGEABEPPRAST; ARIGEABEWA; ARIGEABEWARAST; ARIGEABEWMAST7; ARIGEABFP; ARIGEABFPRAST; ARIGEABGCA; ARIGEABGCARAST; ARIGEABGKMAST7; ARIGEABGMP; ARIGEABGMPRAST; ARIGEABHDMAST7; ARIGEABICMAST7; ARIGEABJAMAST7; ARIGEABJCMAST7; ARIGEABM; ARIGEABMA; ARIGEABMARAST; ARIGEABMMA; ARIGEABMMARAST; ARIGEABMMAST7; ARIGEABMMAST72; ARIGEABMR; ARIGEABMRAST; ARIGEABMRRAST; ARIGEABNMA; ARIGEABNMARAST; ARIGEABNRLMAST7; ARIGEABOGMAST7; ARIGEABOGP; ARIGEABOGPRAST; ARIGEABOMAST7; ARIGEABOTP; ARIGEABOTPRAST; ARIGEABPA; ARIGEABPARAST; ARIGEABPBMAST7; ARIGEABPC; ARIGEABPCRAST; ARIGEABPMAST7; ARIGEABPMAST72; ARIGEABPMAST73; ARIGEABRMAST7; ARIGEABRTP; ARIGEABRTPRAST; ARIGEABSA; ARIGEABSARAST; ARIGEABSBP; ARIGEABSBPRAST; ARIGEABSMA; ARIGEABSMARAST; ARIGEABSMAST7; ARIGEABSSMAST7; ARIGEABSSMAST72; ARIGEABTAA; ARIGEABTAARAST; ARIGEABTAMAST7; ARIGEABTAMAST72; ARIGEABTGMAST7; ARIGEABTGP; ARIGEABTGPRAST; ARIGEABTMAST7; ARIGEABTMP; ARIGEABTMPRAST; ARIGEABTSA; ARIGEABTSARAST; ARIGEABWA; ARIGEABWARAST; ARIGEABWBMAST7; ARIGEABWEP; ARIGEABWEPRAST; ARIGEABWMP; ARIGEABWMPMAST7; ARIGEABWMPRAST; ARIGEABWOP; ARIGEABWOPRAST; ARIGEABWRGP; ARIGEABWRGPRAST; ARIGEABWRP; ARIGEABWRPRAST</t>
         </is>
@@ -2787,7 +2799,8 @@
           <t>binding agent</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>ARIGAABACA; ARIGAABALTERNARIA; ARIGAABBGP; ARIGAABCDA; ARIGAABDDA; ARIGAABEPP; ARIGAABGA; ARIGAABGCA; ARIGAABGMP; ARIGAABMMA; ARIGAABMUCOR; ARIGAABOGP; ARIGAABPENICILLUM; ARIGAABSBP; ARIGAABTGP; ARIGAABWMP; ARIGAABWRP</t>
         </is>
@@ -2817,7 +2830,8 @@
           <t>binding agent; test detail; scale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>ARIGGABAARAST; ARIGGABACA; ARIGGABACARAST; ARIGGABAFRAST; ARIGGABAHDMA; ARIGGABAHDMARAST; ARIGGABAMA; ARIGGABAMARAST; ARIGGABBGP; ARIGGABBGPRAST; ARIGGABBMVA; ARIGGABBMVARAST; ARIGGABCDA; ARIGGABCDARAST; ARIGGABCMA; ARIGGABCMARAST; ARIGGABDDA; ARIGGABDDARAST; ARIGGABDMA; ARIGGABDMARAST; ARIGGABEHDMA; ARIGGABEHDMARAST; ARIGGABEPP; ARIGGABEPPRAST; ARIGGABGA; ARIGGABGCA; ARIGGABGCARAST; ARIGGABGMP; ARIGGABGMPRAST; ARIGGABKLH; ARIGGABMMA; ARIGGABMMARAST; ARIGGABMR; ARIGGABMRPRAST; ARIGGABNMA; ARIGGABNMARAST; ARIGGABOGP; ARIGGABOGPRAST; ARIGGABPFRAST; ARIGGABSBP; ARIGGABSBPRAST; ARIGGABSMA; ARIGGABSMARAST; ARIGGABSTGPRAST; ARIGGABSTMPRAST; ARIGGABSWMPRAST; ARIGGABSWRPRAST; ARIGGABTGP; ARIGGABTMP; ARIGGABWEP; ARIGGABWEPRAST; ARIGGABWMP; ARIGGABWRP</t>
         </is>
@@ -2847,7 +2861,8 @@
           <t>binding agent; scale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>MBIMABA; MBIMABAPN; MBIMABBB; MBIMABBBPN; MBIMABCMV; MBIMABCMVPN; MBIMABCOCC; MBIMABCOCCPN; MBIMABCP; MBIMABCPPN; MBIMABCT; MBIMABCTPN; MBIMABDV; MBIMABDVPN; MBIMABEBVCA; MBIMABEBVCAPN; MBIMABEV; MBIMABEVPN; MBIMABHAV; MBIMABHAVPN; MBIMABHBVCA; MBIMABHBVCAPN; MBIMABHDV; MBIMABHDVPN; MBIMABHEV; MBIMABHEVPN; MBIMABHHV1; MBIMABHHV1PN; MBIMABHHV2; MBIMABHHV2PN; MBIMABHPB19; MBIMABHPB19PN; MBIMABHSV; MBIMABHSVPN; MBIMABLP; MBIMABLPPN; MBIMABMMV; MBIMABMMVPN; MBIMABMP; MBIMABMPPN; MBIMABMRV; MBIMABMRVPN; MBIMABNGLI4; MBIMABNGLI4PN; MBIMABRV; MBIMABRVPN; MBIMABSARSC2; MBIMABSARSC2PN; MBIMABTG; MBIMABTGPN; MBIMABVZV; MBIMABVZVPN</t>
         </is>
@@ -2877,7 +2892,8 @@
           <t>binding agent; scale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>ATIGMABB2G1; ATIGMABB2G1PN; ATIGMABC; ATIGMABCPN; ATIGMABLKMT1A; ATIGMABLKMT1APN; ATIGMABP; ATIGMABPL; ATIGMABPLPN; ATIGMABPPN; ATIGMABTT; ATIGMABTTPN</t>
         </is>
@@ -2907,7 +2923,8 @@
           <t>specimen; method; category; scale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>GLUCBLD; GLUCPE; GLUCPL; GLUCSER; GLUCSERPL; GLUCUA; GLUCURIN; GLUCURINPRES</t>
         </is>
@@ -2937,7 +2954,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>CMONOXBLD; CMONOXEXPAIR</t>
         </is>
@@ -2967,7 +2985,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>NICOTINESERPL; NICOTINEURIN</t>
         </is>
@@ -2997,7 +3016,8 @@
           <t>specimen; category; scale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>BILISERPL; BILIURIN; BILIURINPRES</t>
         </is>
@@ -3027,7 +3047,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>APTTBLD; APTTPPP</t>
         </is>
@@ -3057,7 +3078,8 @@
           <t>specimen; method; category; scale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>RBCBLD; RBCURIN; RBCURINDIP; RBCURINPRES; RBCURINSEDPRES</t>
         </is>
@@ -3087,7 +3109,8 @@
           <t>specimen; method; category; scale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>WBCBLD; WBCURIN; WBCURINDIP; WBCURINPRES; WBCURINSEDPRES</t>
         </is>
@@ -3117,7 +3140,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>PTBLD; PTPPP</t>
         </is>
@@ -3147,7 +3171,8 @@
           <t>specimen; category; scale</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>ALBSERPL; ALBURIN; ALBURINPRES</t>
         </is>
@@ -3177,7 +3202,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>CABLD; CASERPL</t>
         </is>
@@ -3207,7 +3233,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>CKBLD; CKSERPL</t>
         </is>
@@ -3237,7 +3264,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>CLBLD; CLSERPL</t>
         </is>
@@ -3267,7 +3295,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>CO2BLD; CO2SERPL</t>
         </is>
@@ -3297,7 +3326,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>CREATSERPL; CREATURIN</t>
         </is>
@@ -3327,7 +3357,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>INRBLD; INRPPP</t>
         </is>
@@ -3357,7 +3388,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>SODIUMBLD; SODIUMSERPL; SODIUMURIN</t>
         </is>
@@ -3387,7 +3419,8 @@
           <t>scale</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>NITRITEURIN; NITRITEURINPRES; UROBILURINPRES</t>
         </is>
@@ -3417,7 +3450,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>TSHBLD; TSHSERPL</t>
         </is>
@@ -3447,7 +3481,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>VITB12BLD; VITB12SERPL</t>
         </is>
@@ -3477,7 +3512,8 @@
           <t>specimen; category</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>MACROCYBLD; MACROCYURNSED</t>
         </is>
@@ -3507,7 +3543,8 @@
           <t>specimen; category</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>MICROCYBLD; MICROCYURN; MICROCYURNSED</t>
         </is>
@@ -3537,7 +3574,8 @@
           <t>method</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t>HGBBLD; HGBBLDDIP</t>
         </is>
@@ -3567,7 +3605,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
         <is>
           <t>HCGSERPL; HCGURIN</t>
         </is>
@@ -3597,7 +3636,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
         <is>
           <t>KBLD; KSERPL; KURIN</t>
         </is>
@@ -3627,7 +3667,8 @@
           <t>scale</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t>KETONESURIN; KETONESURINPRES</t>
         </is>
@@ -3657,7 +3698,8 @@
           <t>specimen; category; scale</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t>PROTSERPL; PROTURIN; PROTURINPRES</t>
         </is>
@@ -3687,7 +3729,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>VITB9BLD; VITB9SERPL</t>
         </is>
@@ -3717,7 +3760,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
         <is>
           <t>OCCBLDSTOOL; OCCBLDURINPRES</t>
         </is>
@@ -3747,7 +3791,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
         <is>
           <t>TROPONIBLD; TROPONISERPL</t>
         </is>
@@ -3777,7 +3822,8 @@
           <t>specimen</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
         <is>
           <t>CYSTATCSERPL; CYSTATCURIN</t>
         </is>
@@ -3807,7 +3853,8 @@
           <t>test detail; scale</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
         <is>
           <t>HCRNASERPL; HCRNASERPLPRES</t>
         </is>
@@ -3837,7 +3884,8 @@
           <t>test detail; scale</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
         <is>
           <t>HBCAGSERPL; HBCAGSERPLPRES</t>
         </is>
@@ -3867,7 +3915,8 @@
           <t>test detail; scale</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
         <is>
           <t>SAR2RNAQNTCYC; SAR2RNAVIRAL</t>
         </is>
@@ -3897,7 +3946,8 @@
           <t>test detail; scale</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
         <is>
           <t>HBSAGSERPL; HBSAGSERPLPRES</t>
         </is>
@@ -3927,7 +3977,8 @@
           <t>category</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
         <is>
           <t>MEDHISTFREE; MEDHISTPRESP; MHALZHEIMERS; MHBRCADIAG; MHBRCARELAPSE; MHCONFUSIONALEPISODES; MHESSENTIALTREMOR; MHESSENTIALTREMOREXPYR; MHEXTRAPYRAMIDAL; MHFACIALMASKING; MHRIGIDITYUPPEREXTREMITY; MHSENSITIVITYNEUROLEPTICS; MHVISUALHALLUCINATIONS</t>
         </is>
@@ -3957,7 +4008,8 @@
           <t>test detail</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
         <is>
           <t>ESTRCPTAPRPSCORE; ESTRCPTASINTSCORE; ESTRCPTATOTSCORE</t>
         </is>
@@ -3987,7 +4039,8 @@
           <t>test detail</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
         <is>
           <t>PROGESTRAPRPSCORE; PROGESTRASINTSCORE; PROGESTRATOTSCORE</t>
         </is>
@@ -4014,10 +4067,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>location</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>SGJSNSCRFJ; SGJSNSCRHW</t>
         </is>
@@ -4044,10 +4102,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>location; category</t>
+          <t>category</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>RADIATIONCANCER; RADTHERAPHYBREASTCANCER</t>
         </is>
@@ -4077,7 +4140,8 @@
           <t>location</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
         <is>
           <t>MRI; MRIBRAIN</t>
         </is>
@@ -4107,7 +4171,8 @@
           <t>location</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
         <is>
           <t>CTSCAN; CTSCANABDOMIN; CTSCANCHEST; CTSCANPELVIS</t>
         </is>
@@ -4137,7 +4202,8 @@
           <t>location</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
         <is>
           <t>XRAY; XRAYCHEST</t>
         </is>
@@ -4167,7 +4233,8 @@
           <t>location</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
         <is>
           <t>SCINTIGRAPHY; SCINTIGRAPHYBONE</t>
         </is>
@@ -4194,10 +4261,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>category; evaluator</t>
+          <t>category</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
+        <is>
+          <t>evaluator</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>NEWLIND_LUGANO; NEWLIND_RANO</t>
         </is>
@@ -4224,10 +4296,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>category; evaluator</t>
+          <t>category</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
+        <is>
+          <t>evaluator</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>TRGRESP; TRGRESP_LUGANO; TRGRESP_RANO</t>
         </is>
@@ -4254,10 +4331,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>category; evaluator</t>
+          <t>category</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
+        <is>
+          <t>evaluator</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>NTRGRESP; NTRGRESP_LUGANO</t>
         </is>
@@ -4284,10 +4366,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>category; evaluator</t>
+          <t>category</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
+        <is>
+          <t>evaluator</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>OVRLRESP; OVRLRESP_LUGANO; OVRLRESP_RANO</t>
         </is>
@@ -4314,10 +4401,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>CIGARETTEHX; CIGARHX; PIPEHX; TOBACCOHX</t>
         </is>
@@ -4344,10 +4436,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>CAFFEINEHX; COFFEEHX; COLAHX; TEAHIX</t>
         </is>
@@ -4374,10 +4471,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>ALCOHOLHX; BEERHX; DISTILLEDSPIRITSHX; WINEHX</t>
         </is>
@@ -4404,10 +4506,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>evaluator</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>LNSTATE; LNSTATE_RECIST1_1</t>
         </is>
@@ -4434,10 +4541,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>evaluator</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>NEW_TUMSTATE_RECIST1_1; NONNODAL_TUMSTATE_RECIST1_1; TUMSTATE</t>
         </is>
@@ -4464,10 +4576,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>evaluator</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>LDIAM; LDIAM_RECIST1_1</t>
         </is>
@@ -4494,10 +4611,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>evaluator</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>LPERP; LPERP_RECIST1_1</t>
         </is>
@@ -4527,7 +4649,8 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
         <is>
           <t>EGRDMETH; HEGRDMTH</t>
         </is>
@@ -4554,10 +4677,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>evaluator</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>NTIND; NTIND_RECIST1_1</t>
         </is>
@@ -4584,10 +4712,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>evaluator</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>TIND; TIND_RECIST1_1</t>
         </is>
@@ -4617,7 +4750,8 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
         <is>
           <t>TUMERGE; TUMERGE_RECIST1_1</t>
         </is>
@@ -4647,7 +4781,8 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
         <is>
           <t>TUSPLIT; TUSPLIT_RECIST1_1</t>
         </is>
@@ -4677,7 +4812,8 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
         <is>
           <t>TUMIDENT; TUMIDENT_RECIST1_1</t>
         </is>
@@ -4704,10 +4840,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>location</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>SYSBP; SYSBP_EXT</t>
         </is>
@@ -4734,10 +4875,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>location</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>DIABP; DIABP_EXT</t>
         </is>
@@ -4764,10 +4910,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>location</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>PULSE; PULSE_EXT</t>
         </is>
@@ -4794,10 +4945,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>location</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>HR; HR_EXT</t>
         </is>
@@ -4818,32 +4974,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Result_Scales</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>DSSs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>With_Units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Without_Units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -6756,42 +6912,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Claim_ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Claim</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Holds</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -7022,77 +7178,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Observation_Class</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Consumer_Class</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Consumer_Status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>BCs</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>DSSs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>BCs_Fanning_Out</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max_Fanout</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Primary_Axis</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Axes_Seen</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scale_Mix</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Share_With_Units</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Share_With_Specimen</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Share_With_Method</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Share_With_Location</t>
         </is>
@@ -7439,12 +7595,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>location 1</t>
+          <t>(none) 1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7705,7 +7861,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>location 5; category 1</t>
+          <t>location 4; category 1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -7904,12 +8060,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>category 3</t>
+          <t>(none) 3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7961,12 +8117,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>evaluator</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>evaluator 4</t>
+          <t>(none) 4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8080,7 +8236,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>(none) 3; evaluator 2</t>
+          <t>(none) 5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8116,12 +8272,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -8467,7 +8623,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
@@ -8879,7 +9035,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9203,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>category; evaluator</t>
+          <t>category</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9303,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9339,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>evaluator</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9479,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
@@ -9402,12 +9558,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>

--- a/domain-behaviour/interim/Domain_Behaviour.xlsx
+++ b/domain-behaviour/interim/Domain_Behaviour.xlsx
@@ -5571,7 +5571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B164"/>
+  <dimension ref="A1:B168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5829,1111 +5829,1111 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dss:AE</t>
+          <t>variable_meaning_rows</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:AE</t>
+          <t>dss:AE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>primary_axis:AE</t>
+          <t>bcs_fanning_out:AE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dss:BE</t>
+          <t>primary_axis:AE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:BE</t>
+          <t>dss:BE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>primary_axis:BE</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>bcs_fanning_out:BE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dss:CM</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>primary_axis:BE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:CM</t>
+          <t>dss:CM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>primary_axis:CM</t>
+          <t>bcs_fanning_out:CM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dss:DD</t>
+          <t>primary_axis:CM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>category</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:DD</t>
+          <t>dss:DD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>primary_axis:DD</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>bcs_fanning_out:DD</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dss:DM</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>primary_axis:DD</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:DM</t>
+          <t>dss:DM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>primary_axis:DM</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>bcs_fanning_out:DM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dss:DS</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>primary_axis:DM</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:DS</t>
+          <t>dss:DS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>primary_axis:DS</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>bcs_fanning_out:DS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dss:EC</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>primary_axis:DS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:EC</t>
+          <t>dss:EC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>primary_axis:EC</t>
+          <t>bcs_fanning_out:EC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dss:EG</t>
+          <t>primary_axis:EC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:EG</t>
+          <t>dss:EG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>primary_axis:EG</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>bcs_fanning_out:EG</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dss:EX</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>primary_axis:EG</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:EX</t>
+          <t>dss:EX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>primary_axis:EX</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>bcs_fanning_out:EX</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dss:FA</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>primary_axis:EX</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:FA</t>
+          <t>dss:FA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>primary_axis:FA</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>bcs_fanning_out:FA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dss:FT</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>primary_axis:FA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:FT</t>
+          <t>dss:FT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>primary_axis:FT</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>bcs_fanning_out:FT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>dss:GF</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+          <t>primary_axis:FT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:GF</t>
+          <t>dss:GF</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>primary_axis:GF</t>
+          <t>bcs_fanning_out:GF</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>test detail</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dss:IE</t>
+          <t>primary_axis:GF</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>test detail</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:IE</t>
+          <t>dss:IE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>primary_axis:IE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>bcs_fanning_out:IE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dss:IS</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
+          <t>primary_axis:IE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:IS</t>
+          <t>dss:IS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>326</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>primary_axis:IS</t>
+          <t>bcs_fanning_out:IS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>binding agent</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dss:LB</t>
+          <t>primary_axis:IS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>binding agent</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:LB</t>
+          <t>dss:LB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>147</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>primary_axis:LB</t>
+          <t>bcs_fanning_out:LB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>specimen</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dss:MB</t>
+          <t>primary_axis:LB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>specimen</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:MB</t>
+          <t>dss:MB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>primary_axis:MB</t>
+          <t>bcs_fanning_out:MB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>scale; test detail</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dss:MH</t>
+          <t>primary_axis:MB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>scale; test detail</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:MH</t>
+          <t>dss:MH</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>primary_axis:MH</t>
+          <t>bcs_fanning_out:MH</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dss:MI</t>
+          <t>primary_axis:MH</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>category</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:MI</t>
+          <t>dss:MI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>primary_axis:MI</t>
+          <t>bcs_fanning_out:MI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>test detail</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dss:MK</t>
+          <t>primary_axis:MI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>test detail</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:MK</t>
+          <t>dss:MK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>primary_axis:MK</t>
+          <t>bcs_fanning_out:MK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dss:PR</t>
+          <t>primary_axis:MK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:PR</t>
+          <t>dss:PR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>primary_axis:PR</t>
+          <t>bcs_fanning_out:PR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dss:QS</t>
+          <t>primary_axis:PR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>location</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:QS</t>
+          <t>dss:QS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>primary_axis:QS</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>bcs_fanning_out:QS</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>dss:RE</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
+          <t>primary_axis:QS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:RE</t>
+          <t>dss:RE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>primary_axis:RE</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>bcs_fanning_out:RE</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>dss:RP</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+          <t>primary_axis:RE</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:RP</t>
+          <t>dss:RP</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>primary_axis:RP</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>bcs_fanning_out:RP</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>dss:RS</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
+          <t>primary_axis:RP</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:RS</t>
+          <t>dss:RS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>157</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>primary_axis:RS</t>
+          <t>bcs_fanning_out:RS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>dss:SC</t>
+          <t>primary_axis:RS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>category</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:SC</t>
+          <t>dss:SC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>primary_axis:SC</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>bcs_fanning_out:SC</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>dss:SR</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>primary_axis:SC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:SR</t>
+          <t>dss:SR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>primary_axis:SR</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>bcs_fanning_out:SR</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dss:SU</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>primary_axis:SR</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:SU</t>
+          <t>dss:SU</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>primary_axis:SU</t>
+          <t>bcs_fanning_out:SU</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dss:TR</t>
+          <t>primary_axis:SU</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:TR</t>
+          <t>dss:TR</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>primary_axis:TR</t>
+          <t>bcs_fanning_out:TR</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>dss:TS</t>
+          <t>primary_axis:TR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:TS</t>
+          <t>dss:TS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>129</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>primary_axis:TS</t>
+          <t>bcs_fanning_out:TS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dss:TU</t>
+          <t>primary_axis:TS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:TU</t>
+          <t>dss:TU</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>primary_axis:TU</t>
+          <t>bcs_fanning_out:TU</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>dss:UR</t>
+          <t>primary_axis:TU</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:UR</t>
+          <t>dss:UR</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>primary_axis:UR</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>bcs_fanning_out:UR</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>dss:VS</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+          <t>primary_axis:UR</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>bcs_fanning_out:VS</t>
+          <t>dss:VS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>primary_axis:VS</t>
+          <t>bcs_fanning_out:VS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>claim:IS-1</t>
+          <t>primary_axis:VS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>claim:IS-2</t>
+          <t>claim:IS-1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6945,7 +6945,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>claim:GF-1</t>
+          <t>claim:IS-2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6957,7 +6957,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>claim:GF-2</t>
+          <t>claim:GF-1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6969,7 +6969,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>claim:UR-1</t>
+          <t>claim:GF-2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6981,31 +6981,31 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>key_both:specimen</t>
+          <t>claim:UR-1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>key_fanout_only:specimen</t>
+          <t>key_both:specimen</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>key_only:specimen</t>
+          <t>key_fanout_only:specimen</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7017,31 +7017,31 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>key_both:binding agent</t>
+          <t>key_only:specimen</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>key_fanout_only:binding agent</t>
+          <t>key_both:binding agent</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>key_only:binding agent</t>
+          <t>key_fanout_only:binding agent</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7053,31 +7053,31 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>key_both:test detail</t>
+          <t>key_only:binding agent</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>key_fanout_only:test detail</t>
+          <t>key_both:test detail</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>key_only:test detail</t>
+          <t>key_fanout_only:test detail</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7089,115 +7089,115 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>key_both:method</t>
+          <t>key_only:test detail</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>key_fanout_only:method</t>
+          <t>key_both:method</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>key_only:method</t>
+          <t>key_fanout_only:method</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>key_both:scale</t>
+          <t>key_only:method</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>key_fanout_only:scale</t>
+          <t>key_both:scale</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>key_only:scale</t>
+          <t>key_fanout_only:scale</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>key_both:category</t>
+          <t>key_only:scale</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>key_fanout_only:category</t>
+          <t>key_both:category</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>key_only:category</t>
+          <t>key_fanout_only:category</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>key_both:location</t>
+          <t>key_only:category</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7209,7 +7209,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>key_fanout_only:location</t>
+          <t>key_both:location</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7221,7 +7221,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>key_only:location</t>
+          <t>key_fanout_only:location</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7233,7 +7233,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>key_both:evaluator</t>
+          <t>key_only:location</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7245,7 +7245,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>key_fanout_only:evaluator</t>
+          <t>key_both:evaluator</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7257,7 +7257,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>key_only:evaluator</t>
+          <t>key_fanout_only:evaluator</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7269,7 +7269,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>key_both:test code</t>
+          <t>key_only:evaluator</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7281,7 +7281,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>key_fanout_only:test code</t>
+          <t>key_both:test code</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7293,31 +7293,31 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>key_only:test code</t>
+          <t>key_fanout_only:test code</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>key_both:object</t>
+          <t>key_only:test code</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>key_fanout_only:object</t>
+          <t>key_both:object</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7329,7 +7329,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>key_only:object</t>
+          <t>key_fanout_only:object</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7341,67 +7341,67 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>key_grain:one key per DSS</t>
+          <t>key_only:object</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>key_grain:one key for all DSSs</t>
+          <t>key_grain:one key per DSS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>key_grain:in between</t>
+          <t>key_grain:one key for all DSSs</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>loinc_both:specimen/system</t>
+          <t>key_grain:in between</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>loinc_cosmos_only:specimen/system</t>
+          <t>loinc_both:specimen/system</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>loinc_only:specimen/system</t>
+          <t>loinc_cosmos_only:specimen/system</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7413,72 +7413,120 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>loinc_both:method/method</t>
+          <t>loinc_only:specimen/system</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>loinc_cosmos_only:method/method</t>
+          <t>loinc_both:method/method</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>loinc_only:method/method</t>
+          <t>loinc_cosmos_only:method/method</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>loinc_both:scale/scale</t>
+          <t>loinc_only:method/method</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>loinc_cosmos_only:scale/scale</t>
+          <t>loinc_both:scale/scale</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>loinc_cosmos_only:scale/scale</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
           <t>loinc_only:scale/scale</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>variable_meaning:sources agree</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>variable_meaning:sources disagree, decided by a stated rule</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>variable_meaning:standards silent, open</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7600,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01 11:31</t>
+          <t>2026-10-08 07:55</t>
         </is>
       </c>
     </row>

--- a/domain-behaviour/interim/Domain_Behaviour.xlsx
+++ b/domain-behaviour/interim/Domain_Behaviour.xlsx
@@ -2161,14 +2161,10 @@
           <t>Findings</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Specimen</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>excluded from Specimen_Findings</t>
+          <t>no consumer class</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4541,7 +4537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4751,48 +4747,6 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>Test-detail-driven, not specimen-driven: the DSSs of one BC differ by test detail (TSTDTL). The March 2026 analysis recorded it as scale-driven.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Specimen_Findings</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>UR-1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>No BC has more than one DSS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>no_fanout</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0 BCs fan out</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Zero decomposition despite Specimen_Based metadata flag.</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5888,6 +5842,55 @@
       </c>
       <c r="O20" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>no consumer class</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Quantitative 5; Nominal 4; Narrative 1</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -5901,7 +5904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B174"/>
+  <dimension ref="A1:B173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5984,7 +5987,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6023,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -7383,31 +7386,31 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>claim:UR-1</t>
+          <t>key_both:specimen</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>key_both:specimen</t>
+          <t>key_fanout_only:specimen</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>key_fanout_only:specimen</t>
+          <t>key_only:specimen</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7419,31 +7422,31 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>key_only:specimen</t>
+          <t>key_both:binding agent</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>key_both:binding agent</t>
+          <t>key_fanout_only:binding agent</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>key_fanout_only:binding agent</t>
+          <t>key_only:binding agent</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7455,31 +7458,31 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>key_only:binding agent</t>
+          <t>key_both:test detail</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>key_both:test detail</t>
+          <t>key_fanout_only:test detail</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>key_fanout_only:test detail</t>
+          <t>key_only:test detail</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7491,115 +7494,115 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>key_only:test detail</t>
+          <t>key_both:method</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>key_both:method</t>
+          <t>key_fanout_only:method</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>key_fanout_only:method</t>
+          <t>key_only:method</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>key_only:method</t>
+          <t>key_both:scale</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>key_both:scale</t>
+          <t>key_fanout_only:scale</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>key_fanout_only:scale</t>
+          <t>key_only:scale</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>key_only:scale</t>
+          <t>key_both:category</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>key_both:category</t>
+          <t>key_fanout_only:category</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>key_fanout_only:category</t>
+          <t>key_only:category</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>key_only:category</t>
+          <t>key_both:location</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7611,7 +7614,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>key_both:location</t>
+          <t>key_fanout_only:location</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7623,7 +7626,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>key_fanout_only:location</t>
+          <t>key_only:location</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7635,7 +7638,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>key_only:location</t>
+          <t>key_both:evaluator</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7647,7 +7650,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>key_both:evaluator</t>
+          <t>key_fanout_only:evaluator</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7659,7 +7662,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>key_fanout_only:evaluator</t>
+          <t>key_only:evaluator</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7671,7 +7674,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>key_only:evaluator</t>
+          <t>key_both:test code</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7683,7 +7686,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>key_both:test code</t>
+          <t>key_fanout_only:test code</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7695,31 +7698,31 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>key_fanout_only:test code</t>
+          <t>key_only:test code</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>key_only:test code</t>
+          <t>key_both:object</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>key_both:object</t>
+          <t>key_fanout_only:object</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7731,7 +7734,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>key_fanout_only:object</t>
+          <t>key_only:object</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7743,67 +7746,67 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>key_only:object</t>
+          <t>key_grain:one key per DSS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>key_grain:one key per DSS</t>
+          <t>key_grain:one key for all DSSs</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>key_grain:one key for all DSSs</t>
+          <t>key_grain:in between</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>key_grain:in between</t>
+          <t>loinc_both:specimen/system</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>loinc_both:specimen/system</t>
+          <t>loinc_cosmos_only:specimen/system</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>loinc_cosmos_only:specimen/system</t>
+          <t>loinc_only:specimen/system</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7815,118 +7818,106 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>loinc_only:specimen/system</t>
+          <t>loinc_both:method/method</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>loinc_both:method/method</t>
+          <t>loinc_cosmos_only:method/method</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>loinc_cosmos_only:method/method</t>
+          <t>loinc_only:method/method</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>loinc_only:method/method</t>
+          <t>loinc_both:scale/scale</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>loinc_both:scale/scale</t>
+          <t>loinc_cosmos_only:scale/scale</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>loinc_cosmos_only:scale/scale</t>
+          <t>loinc_only:scale/scale</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>loinc_only:scale/scale</t>
+          <t>variable_meaning:sources agree</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>variable_meaning:sources agree</t>
+          <t>variable_meaning:sources disagree, decided by a stated rule</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>variable_meaning:sources disagree, decided by a stated rule</t>
+          <t>variable_meaning:standards silent, open</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>variable_meaning:standards silent, open</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -8002,7 +7993,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 11:48</t>
+          <t>2026-10-12 15:05</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8029,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 11:49</t>
+          <t>2026-10-12 17:03</t>
         </is>
       </c>
     </row>
